--- a/01_analyses_states/Meghalaya/results/SoIB_summaries.xlsx
+++ b/01_analyses_states/Meghalaya/results/SoIB_summaries.xlsx
@@ -461,7 +461,7 @@
         <v>0</v>
       </c>
       <c r="C7">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8">
@@ -471,10 +471,10 @@
         </is>
       </c>
       <c r="B8">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C8">
-        <v>361</v>
+        <v>358</v>
       </c>
     </row>
   </sheetData>
@@ -613,7 +613,7 @@
         </is>
       </c>
       <c r="B4">
-        <v>554</v>
+        <v>553</v>
       </c>
     </row>
   </sheetData>
@@ -650,7 +650,7 @@
         </is>
       </c>
       <c r="B2">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="3">
@@ -673,7 +673,7 @@
         </is>
       </c>
       <c r="B4">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C4">
         <v>0</v>

--- a/01_analyses_states/Meghalaya/results/SoIB_summaries.xlsx
+++ b/01_analyses_states/Meghalaya/results/SoIB_summaries.xlsx
@@ -471,10 +471,10 @@
         </is>
       </c>
       <c r="B8">
-        <v>370</v>
+        <v>363</v>
       </c>
       <c r="C8">
-        <v>358</v>
+        <v>351</v>
       </c>
     </row>
   </sheetData>
@@ -603,7 +603,7 @@
         </is>
       </c>
       <c r="B3">
-        <v>286</v>
+        <v>387</v>
       </c>
     </row>
     <row r="4">
@@ -613,7 +613,7 @@
         </is>
       </c>
       <c r="B4">
-        <v>553</v>
+        <v>441</v>
       </c>
     </row>
   </sheetData>
@@ -650,7 +650,7 @@
         </is>
       </c>
       <c r="B2">
-        <v>370</v>
+        <v>363</v>
       </c>
     </row>
     <row r="3">
@@ -742,7 +742,7 @@
         <v>92</v>
       </c>
       <c r="E2">
-        <v>93.90000000000001</v>
+        <v>92.90000000000001</v>
       </c>
     </row>
     <row r="3">
@@ -758,10 +758,10 @@
         <v>10.7</v>
       </c>
       <c r="D3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E3">
-        <v>6.1</v>
+        <v>7.1</v>
       </c>
     </row>
   </sheetData>
